--- a/src/app/modules/dashboard/excel_files/whole-food-plant-based-fruit-dishes.xlsx
+++ b/src/app/modules/dashboard/excel_files/whole-food-plant-based-fruit-dishes.xlsx
@@ -587,7 +587,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -597,7 +597,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -790,7 +790,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -800,7 +800,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1516,7 +1516,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2018,7 +2018,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2107,7 +2107,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2308,7 +2308,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2419,7 +2419,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2509,7 +2509,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2519,7 +2519,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2620,7 +2620,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2722,7 +2722,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2812,7 +2812,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2822,7 +2822,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -3009,7 +3009,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3019,7 +3019,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3118,7 +3118,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3215,7 +3215,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3405,7 +3405,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3415,7 +3415,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3504,7 +3504,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3604,7 +3604,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -3614,7 +3614,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -3715,7 +3715,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3804,7 +3804,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3814,7 +3814,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3903,7 +3903,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -3913,7 +3913,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -4002,7 +4002,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4012,7 +4012,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4316,7 +4316,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -4405,7 +4405,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4415,7 +4415,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -4505,7 +4505,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -4515,7 +4515,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -4605,7 +4605,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -4615,7 +4615,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -4704,7 +4704,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -4714,7 +4714,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -4803,7 +4803,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -4813,7 +4813,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -4903,7 +4903,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -4913,7 +4913,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -5002,7 +5002,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5012,7 +5012,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -5100,7 +5100,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -5110,7 +5110,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5208,7 +5208,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -5395,7 +5395,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -5405,7 +5405,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -5494,7 +5494,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -5504,7 +5504,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -5602,7 +5602,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -5690,7 +5690,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -5700,7 +5700,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -5788,7 +5788,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -5798,7 +5798,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -5887,7 +5887,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -5985,7 +5985,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -5995,7 +5995,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -6084,7 +6084,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -6094,7 +6094,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -6183,7 +6183,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -6193,7 +6193,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -6280,7 +6280,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -6290,7 +6290,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -6377,7 +6377,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -6387,7 +6387,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -6476,7 +6476,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -6486,7 +6486,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -6577,7 +6577,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -6587,7 +6587,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -6678,7 +6678,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -6688,7 +6688,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -6778,7 +6778,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -6788,7 +6788,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -6876,7 +6876,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -6886,7 +6886,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -6976,7 +6976,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -6986,7 +6986,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -7077,7 +7077,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -7175,7 +7175,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -7185,7 +7185,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -7272,7 +7272,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -7282,7 +7282,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -7369,7 +7369,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -7466,7 +7466,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -7476,7 +7476,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -7565,7 +7565,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -7575,7 +7575,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -7664,7 +7664,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -7674,7 +7674,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -7773,7 +7773,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -7862,7 +7862,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -7872,7 +7872,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -7961,7 +7961,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -7971,7 +7971,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -8060,7 +8060,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -8158,7 +8158,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -8168,7 +8168,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -8255,7 +8255,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -8265,7 +8265,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -8351,7 +8351,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -8361,7 +8361,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -8447,7 +8447,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -8457,7 +8457,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -8544,7 +8544,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -8554,7 +8554,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -8642,7 +8642,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -8652,7 +8652,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -8739,7 +8739,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -8749,7 +8749,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -8835,7 +8835,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -8845,7 +8845,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -8933,7 +8933,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -8943,7 +8943,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -9032,7 +9032,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -9042,7 +9042,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -9130,7 +9130,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -9140,7 +9140,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -9227,7 +9227,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -9237,7 +9237,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -9325,7 +9325,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -9335,7 +9335,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -9424,7 +9424,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -9434,7 +9434,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -9522,7 +9522,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -9532,7 +9532,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -9620,7 +9620,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -9630,7 +9630,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -9718,7 +9718,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -9728,7 +9728,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -9816,7 +9816,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -9914,7 +9914,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -9924,7 +9924,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -10011,7 +10011,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -10021,7 +10021,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -10107,7 +10107,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -10117,7 +10117,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -10202,7 +10202,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -10212,7 +10212,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -10299,7 +10299,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -10309,7 +10309,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -10398,7 +10398,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -10408,7 +10408,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
